--- a/Readership Reports/Places.xlsx
+++ b/Readership Reports/Places.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Readership-Word-Cloud/Readership Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Continuous-Word-Cloud/Readership Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90935E96-8C7B-2849-A1EE-2DF402D257CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0495F57B-6421-274A-9225-37EB4CA24E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="14260" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="416">
   <si>
     <t>Vancouver</t>
   </si>
@@ -1218,13 +1218,79 @@
   </si>
   <si>
     <t>Scheuer Facundo Agustin</t>
+  </si>
+  <si>
+    <t>Bogota, Colombia</t>
+  </si>
+  <si>
+    <t>Venda Nova, Brazil</t>
+  </si>
+  <si>
+    <t>Faridabad, India</t>
+  </si>
+  <si>
+    <t>Lang Long Son, Vietnam</t>
+  </si>
+  <si>
+    <t>Nam Thanh, Vietnam</t>
+  </si>
+  <si>
+    <t>Haikou, China</t>
+  </si>
+  <si>
+    <t>Yen Bai, Vietnam</t>
+  </si>
+  <si>
+    <t>Yuxi, China</t>
+  </si>
+  <si>
+    <t>Yangjiang, China</t>
+  </si>
+  <si>
+    <t>Zhaoqing, China</t>
+  </si>
+  <si>
+    <t>Yibin, China</t>
+  </si>
+  <si>
+    <t>Meishan, China</t>
+  </si>
+  <si>
+    <t>Lanzhou, China</t>
+  </si>
+  <si>
+    <t>Shangluo, China</t>
+  </si>
+  <si>
+    <t>Huaibei, China</t>
+  </si>
+  <si>
+    <t>Zibo, China</t>
+  </si>
+  <si>
+    <t>Datong, China</t>
+  </si>
+  <si>
+    <t>Shoreline, WA</t>
+  </si>
+  <si>
+    <t>Birmingham, AL</t>
+  </si>
+  <si>
+    <t>Denver, PA</t>
+  </si>
+  <si>
+    <t>Keyport, NJ</t>
+  </si>
+  <si>
+    <t>Stamford, CT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1237,6 +1303,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1259,9 +1331,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1596,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAC4019-EF2D-7E46-9CD0-5ADF4300B4E4}">
-  <dimension ref="A1:B368"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -3529,6 +3602,121 @@
         <v>392</v>
       </c>
     </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A369" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A370" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A371" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A372" s="1" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A373" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A374" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A375" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A376" s="1" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A377" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A378" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A379" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A380" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A381" s="1" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A382" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A383" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A384" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A385" s="1" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A386" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A387" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A388" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A389" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A390" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A391" s="2" t="s">
+        <v>415</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Readership Reports/Places.xlsx
+++ b/Readership Reports/Places.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewmacpherson/development/GitHub/Continuous-Word-Cloud/Readership Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0495F57B-6421-274A-9225-37EB4CA24E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F950940-3EB3-1647-A99B-31333FAA09C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="14260" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
+    <workbookView xWindow="-28800" yWindow="22100" windowWidth="14260" windowHeight="15560" xr2:uid="{836667C0-DE47-B041-8E18-FB71019D3FBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="452">
   <si>
     <t>Vancouver</t>
   </si>
@@ -1283,7 +1283,115 @@
     <t>Keyport, NJ</t>
   </si>
   <si>
-    <t>Stamford, CT</t>
+    <t>Slidell, LA</t>
+  </si>
+  <si>
+    <t>Little Rock</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Mount Laurel, NJ</t>
+  </si>
+  <si>
+    <t>Eatontown, NJ</t>
+  </si>
+  <si>
+    <t>Piscataway, NJ</t>
+  </si>
+  <si>
+    <t>Secaucus, NJ</t>
+  </si>
+  <si>
+    <t>Scranton, PA</t>
+  </si>
+  <si>
+    <t>Ipswich, MA</t>
+  </si>
+  <si>
+    <t>Fez, Morocco</t>
+  </si>
+  <si>
+    <t>Dundee, Scotland</t>
+  </si>
+  <si>
+    <t>Midrand, South Africa</t>
+  </si>
+  <si>
+    <t>Pando, Uruguay</t>
+  </si>
+  <si>
+    <t>Mudukulattur, India</t>
+  </si>
+  <si>
+    <t>Panipat, India</t>
+  </si>
+  <si>
+    <t>Kota, India</t>
+  </si>
+  <si>
+    <t>Lincang, China</t>
+  </si>
+  <si>
+    <t>Hung Yen, Vietnam</t>
+  </si>
+  <si>
+    <t>Tuy Hoa, Vietnam</t>
+  </si>
+  <si>
+    <t>Phu Quoc, Vietnam</t>
+  </si>
+  <si>
+    <t>Can Duoc, Vietnam</t>
+  </si>
+  <si>
+    <t>Haiphong, Vietnam</t>
+  </si>
+  <si>
+    <t>Bijie, China</t>
+  </si>
+  <si>
+    <t>Maoming, China</t>
+  </si>
+  <si>
+    <t>Foshan, China</t>
+  </si>
+  <si>
+    <t>Qingyuan, China</t>
+  </si>
+  <si>
+    <t>Xiamen, China</t>
+  </si>
+  <si>
+    <t>Jiangxi, China</t>
+  </si>
+  <si>
+    <t>Yichun, China</t>
+  </si>
+  <si>
+    <t>Lishui, China</t>
+  </si>
+  <si>
+    <t>Huangshi, China</t>
+  </si>
+  <si>
+    <t>Tongling, China</t>
+  </si>
+  <si>
+    <t>Anhui, China</t>
+  </si>
+  <si>
+    <t>Nanjing, China</t>
+  </si>
+  <si>
+    <t>Nantong, China</t>
+  </si>
+  <si>
+    <t>Haidong, China</t>
+  </si>
+  <si>
+    <t>Ulanqab, China</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1777,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAC4019-EF2D-7E46-9CD0-5ADF4300B4E4}">
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B428"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.6640625" bestFit="1" customWidth="1"/>
@@ -3717,6 +3825,191 @@
         <v>415</v>
       </c>
     </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A392" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A393" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A394" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A395" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A396" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A397" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A398" s="2" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A399" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A400" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A401" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A402" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A403" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A404" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A405" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A406" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A407" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A408" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A409" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A410" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A411" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A412" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A413" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A414" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A415" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A416" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A417" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A418" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A419" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A420" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A421" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A422" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A423" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A424" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A425" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A426" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A427" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A428" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
